--- a/data/interim/model_e_dataset.xlsx
+++ b/data/interim/model_e_dataset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1267"/>
+  <dimension ref="A1:M1274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67581,6 +67581,377 @@
         </is>
       </c>
     </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>PFP</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>L-proline</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>147-85-3</t>
+        </is>
+      </c>
+      <c r="E1268" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="F1268" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>matrix ID PFP 1</t>
+        </is>
+      </c>
+      <c r="H1268" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1268" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1268" t="inlineStr">
+        <is>
+          <t>C1C[C@H](NC1)C(=O)O</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>BlueBird</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>2-amino-4,6-dihydroxypyrimidine</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>56-09-7</t>
+        </is>
+      </c>
+      <c r="E1269" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="F1269" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>matrix ID BlueBird 1</t>
+        </is>
+      </c>
+      <c r="H1269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1269" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1269" t="inlineStr">
+        <is>
+          <t>C1=C(N=C(NC1=O)N)O</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>BlueBird</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>L-Cystine</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>56-89-3</t>
+        </is>
+      </c>
+      <c r="E1270" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1270" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>matrix ID BlueBird 1</t>
+        </is>
+      </c>
+      <c r="H1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1270" t="inlineStr">
+        <is>
+          <t>C([C@@H](C(=O)O)N)SSC[C@@H](C(=O)O)N</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>BlueBird</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>caffeine</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>58-08-2</t>
+        </is>
+      </c>
+      <c r="E1271" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="F1271" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>matrix ID BlueBird 1</t>
+        </is>
+      </c>
+      <c r="H1271" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1271" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1271" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1271" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1271" t="inlineStr">
+        <is>
+          <t>CN1C=NC2=C1C(=O)N(C(=O)N2C)C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>BlueBird</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>triphenylphospine</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>603-35-0</t>
+        </is>
+      </c>
+      <c r="E1272" t="n">
+        <v>6.345</v>
+      </c>
+      <c r="F1272" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>matrix ID BlueBird 1</t>
+        </is>
+      </c>
+      <c r="H1272" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1272" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1272" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1272" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1272" t="inlineStr">
+        <is>
+          <t>C1=CC=C(C=C1)P(C2=CC=CC=C2)C3=CC=CC=C3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>BlueBird</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Indol acetic acid</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>87-51-4</t>
+        </is>
+      </c>
+      <c r="E1273" t="n">
+        <v>4.083</v>
+      </c>
+      <c r="F1273" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>matrix ID BlueBird 1</t>
+        </is>
+      </c>
+      <c r="H1273" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1273" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1273" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1273" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1273" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1273" t="inlineStr">
+        <is>
+          <t>C1=CC=C2C(=C1)C(=CN2)CC(=O)O</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>PFP</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>2-2-bis(diphenylphosphino)1.1-binaphthyl</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>98327-87-8</t>
+        </is>
+      </c>
+      <c r="E1274" t="n">
+        <v>6.786</v>
+      </c>
+      <c r="F1274" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>matrix ID PFP 1</t>
+        </is>
+      </c>
+      <c r="H1274" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1274" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1274" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1274" t="inlineStr">
+        <is>
+          <t>C1=CC=C(C=C1)P(C2=CC=CC=C2)C3=C(C4=CC=CC=C4C=C3)C5=C(C=CC6=CC=CC=C65)P(C7=CC=CC=C7)C8=CC=CC=C8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
